--- a/생활속의통계/Excel/202204013변하연_2주차 데이터 0907.xlsx
+++ b/생활속의통계/Excel/202204013변하연_2주차 데이터 0907.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FAC38C-C685-42E8-A40A-89281F80B2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE922AAC-A856-49DE-AF8D-DFBC0A74C333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{F6403738-FB68-43CE-8571-B04BDB7D9E84}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="5" xr2:uid="{F6403738-FB68-43CE-8571-B04BDB7D9E84}"/>
   </bookViews>
   <sheets>
     <sheet name="예제1" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>계급구간</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,9 @@
     <t>계급 구간</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>기타</t>
+  </si>
 </sst>
 </file>
 
@@ -290,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -309,13 +312,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -366,6 +378,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5895,13 +5919,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB816F-FF85-47F3-91BE-354DC2CE6D22}">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="5" max="5" width="12.3125" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -5909,7 +5933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>50</v>
       </c>
@@ -5917,12 +5941,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>36</v>
       </c>
@@ -5934,7 +5958,7 @@
         <v>6.324555320336759</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>40</v>
       </c>
@@ -5946,7 +5970,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>45</v>
       </c>
@@ -5958,7 +5982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:9" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>60</v>
       </c>
@@ -5969,7 +5993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>76</v>
       </c>
@@ -5980,7 +6004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>100</v>
       </c>
@@ -5991,7 +6015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>78</v>
       </c>
@@ -6008,7 +6032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>40</v>
       </c>
@@ -6022,7 +6046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>30</v>
       </c>
@@ -6036,7 +6060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>50</v>
       </c>
@@ -6050,7 +6074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>48</v>
       </c>
@@ -6064,7 +6088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>40</v>
       </c>
@@ -6072,133 +6096,133 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>63</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>80</v>
       </c>
@@ -6217,13 +6241,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACD7761-ECC5-49D6-ACC9-949D277C94E0}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.1875" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>3</v>
       </c>
@@ -6234,7 +6258,7 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -6243,7 +6267,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -6252,7 +6276,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -6261,7 +6285,7 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>60</v>
       </c>
@@ -6273,7 +6297,7 @@
         <v>6.324555320336759</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>30</v>
       </c>
@@ -6285,7 +6309,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>15</v>
       </c>
@@ -6297,7 +6321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>90</v>
       </c>
@@ -6309,7 +6333,7 @@
         <v>15.020818885799802</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>40</v>
       </c>
@@ -6321,7 +6345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>50</v>
       </c>
@@ -6338,7 +6362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>60</v>
       </c>
@@ -6352,7 +6376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>20</v>
       </c>
@@ -6366,7 +6390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>90</v>
       </c>
@@ -6380,7 +6404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>100</v>
       </c>
@@ -6394,7 +6418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>110</v>
       </c>
@@ -6408,7 +6432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>40</v>
       </c>
@@ -6422,149 +6446,203 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>80</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G23" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>40</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G24" s="17">
+        <v>30</v>
+      </c>
+      <c r="H24" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>35</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G25" s="17">
+        <v>45</v>
+      </c>
+      <c r="H25" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G26" s="17">
+        <v>60</v>
+      </c>
+      <c r="H26" s="18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G27" s="17">
+        <v>75</v>
+      </c>
+      <c r="H27" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G28" s="17">
+        <v>90</v>
+      </c>
+      <c r="H28" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G29" s="17">
+        <v>105</v>
+      </c>
+      <c r="H29" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G30" s="17">
+        <v>120</v>
+      </c>
+      <c r="H30" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="G31" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G11:G17">
-    <sortCondition ref="G11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G24:G30">
+    <sortCondition ref="G24"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:G4"/>
@@ -6579,12 +6657,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E1142B-865F-48E9-A671-0BE61763FAB6}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.1875" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
@@ -6595,7 +6673,7 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -6604,7 +6682,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -6613,7 +6691,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -6622,7 +6700,7 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -6640,7 +6718,7 @@
         <v>5.4772255750516612</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6658,7 +6736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -6676,7 +6754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -6694,7 +6772,7 @@
         <v>1.8257418583505538</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -6711,7 +6789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6734,7 +6812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -6754,7 +6832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8</v>
       </c>
@@ -6774,7 +6852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6794,7 +6872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5</v>
       </c>
@@ -6830,9 +6908,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8691C07-8DB3-4E4C-8EA3-9DB6F93A3F39}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -6840,7 +6918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6848,7 +6926,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6856,7 +6934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6864,7 +6942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6872,7 +6950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6890,13 +6968,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D106A382-852C-48ED-A521-1C7EF762279D}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
@@ -6908,7 +6986,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -6918,7 +6996,7 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -6928,12 +7006,12 @@
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -6941,7 +7019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>43831</v>
       </c>
@@ -6949,7 +7027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>43862</v>
       </c>
@@ -6960,7 +7038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>43891</v>
       </c>
@@ -6971,7 +7049,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>43922</v>
       </c>
@@ -6982,7 +7060,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>43952</v>
       </c>
@@ -6993,7 +7071,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>43983</v>
       </c>
@@ -7004,7 +7082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>44013</v>
       </c>
@@ -7015,7 +7093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>44044</v>
       </c>
@@ -7026,7 +7104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>44075</v>
       </c>
@@ -7037,7 +7115,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>44105</v>
       </c>
@@ -7048,7 +7126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>44136</v>
       </c>
@@ -7059,7 +7137,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>44166</v>
       </c>
@@ -7070,7 +7148,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>44197</v>
       </c>
@@ -7081,7 +7159,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>44228</v>
       </c>
@@ -7092,7 +7170,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>44256</v>
       </c>
@@ -7103,7 +7181,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -7121,9 +7199,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8A5689-E2FA-457E-8301-11D5C801C7EB}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
@@ -7135,7 +7213,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -7145,7 +7223,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -7155,7 +7233,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -7163,7 +7241,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7171,7 +7249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -7179,7 +7257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -7187,7 +7265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7195,7 +7273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>

--- a/생활속의통계/Excel/202204013변하연_2주차 데이터 0907.xlsx
+++ b/생활속의통계/Excel/202204013변하연_2주차 데이터 0907.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE922AAC-A856-49DE-AF8D-DFBC0A74C333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A1C71A-5C18-4FED-BADB-DE02922076D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="5" xr2:uid="{F6403738-FB68-43CE-8571-B04BDB7D9E84}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{F6403738-FB68-43CE-8571-B04BDB7D9E84}"/>
   </bookViews>
   <sheets>
     <sheet name="예제1" sheetId="13" r:id="rId1"/>
@@ -327,7 +327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -364,6 +364,9 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -378,18 +381,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5919,13 +5910,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB816F-FF85-47F3-91BE-354DC2CE6D22}">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -5933,7 +5924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" s="3">
         <v>50</v>
       </c>
@@ -5941,12 +5932,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" s="3">
         <v>36</v>
       </c>
@@ -5958,7 +5949,7 @@
         <v>6.324555320336759</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>40</v>
       </c>
@@ -5970,7 +5961,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" s="3">
         <v>45</v>
       </c>
@@ -5982,7 +5973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A7" s="3">
         <v>60</v>
       </c>
@@ -5993,7 +5984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" s="3">
         <v>76</v>
       </c>
@@ -6004,7 +5995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>100</v>
       </c>
@@ -6015,7 +6006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" s="3">
         <v>78</v>
       </c>
@@ -6032,7 +6023,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" s="3">
         <v>40</v>
       </c>
@@ -6046,7 +6037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" s="3">
         <v>30</v>
       </c>
@@ -6060,7 +6051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A13" s="3">
         <v>50</v>
       </c>
@@ -6074,7 +6065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A14" s="3">
         <v>48</v>
       </c>
@@ -6088,7 +6079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A15" s="3">
         <v>40</v>
       </c>
@@ -6096,133 +6087,133 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A16" s="3">
         <v>63</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A17" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A18" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A19" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A20" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A21" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A22" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A23" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A24" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A25" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A26" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A27" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A28" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A29" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A30" s="3">
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A31" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A32" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A33" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A34" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A35" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A36" s="3">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A37" s="3">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A38" s="3">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A39" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A40" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A41" s="3">
         <v>80</v>
       </c>
@@ -6241,51 +6232,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACD7761-ECC5-49D6-ACC9-949D277C94E0}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>60</v>
       </c>
@@ -6297,7 +6288,7 @@
         <v>6.324555320336759</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>30</v>
       </c>
@@ -6309,7 +6300,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>15</v>
       </c>
@@ -6321,7 +6312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A9">
         <v>90</v>
       </c>
@@ -6333,7 +6324,7 @@
         <v>15.020818885799802</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>40</v>
       </c>
@@ -6345,7 +6336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>50</v>
       </c>
@@ -6362,7 +6353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>60</v>
       </c>
@@ -6376,7 +6367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>20</v>
       </c>
@@ -6390,7 +6381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>90</v>
       </c>
@@ -6404,7 +6395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>100</v>
       </c>
@@ -6418,7 +6409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>110</v>
       </c>
@@ -6432,7 +6423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>40</v>
       </c>
@@ -6446,196 +6437,196 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A22">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A24">
         <v>40</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24">
         <v>30</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A25">
         <v>35</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25">
         <v>45</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>20</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26">
         <v>60</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A27">
         <v>30</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27">
         <v>75</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A28">
         <v>100</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28">
         <v>90</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A29">
         <v>80</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29">
         <v>105</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A30">
         <v>40</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30">
         <v>120</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A31">
         <v>50</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A33">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A34">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A35">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A36">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A38">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A39">
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A40">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A41">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A42">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A43">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A45">
         <v>40</v>
       </c>
@@ -6657,50 +6648,50 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E1142B-865F-48E9-A671-0BE61763FAB6}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="6" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -6718,7 +6709,7 @@
         <v>5.4772255750516612</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6736,7 +6727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>2</v>
       </c>
@@ -6754,7 +6745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A9">
         <v>3</v>
       </c>
@@ -6772,7 +6763,7 @@
         <v>1.8257418583505538</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>7</v>
       </c>
@@ -6789,7 +6780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6812,7 +6803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>12</v>
       </c>
@@ -6832,7 +6823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>8</v>
       </c>
@@ -6852,7 +6843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6872,7 +6863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>5</v>
       </c>
@@ -6908,9 +6899,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8691C07-8DB3-4E4C-8EA3-9DB6F93A3F39}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -6918,7 +6909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6926,7 +6917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6934,7 +6925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6942,7 +6933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6950,7 +6941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6968,50 +6959,50 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D106A382-852C-48ED-A521-1C7EF762279D}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -7019,7 +7010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A6" s="7">
         <v>43831</v>
       </c>
@@ -7027,7 +7018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A7" s="7">
         <v>43862</v>
       </c>
@@ -7038,7 +7029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A8" s="7">
         <v>43891</v>
       </c>
@@ -7049,7 +7040,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A9" s="7">
         <v>43922</v>
       </c>
@@ -7060,7 +7051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A10" s="7">
         <v>43952</v>
       </c>
@@ -7071,7 +7062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A11" s="7">
         <v>43983</v>
       </c>
@@ -7082,7 +7073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A12" s="7">
         <v>44013</v>
       </c>
@@ -7093,7 +7084,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A13" s="7">
         <v>44044</v>
       </c>
@@ -7104,7 +7095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A14" s="7">
         <v>44075</v>
       </c>
@@ -7115,7 +7106,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A15" s="7">
         <v>44105</v>
       </c>
@@ -7126,7 +7117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A16" s="7">
         <v>44136</v>
       </c>
@@ -7137,7 +7128,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A17" s="7">
         <v>44166</v>
       </c>
@@ -7148,7 +7139,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A18" s="7">
         <v>44197</v>
       </c>
@@ -7159,7 +7150,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A19" s="7">
         <v>44228</v>
       </c>
@@ -7170,7 +7161,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A20" s="7">
         <v>44256</v>
       </c>
@@ -7181,7 +7172,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -7199,41 +7190,41 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8A5689-E2FA-457E-8301-11D5C801C7EB}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -7241,7 +7232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7249,7 +7240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -7257,7 +7248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -7265,7 +7256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7273,7 +7264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>22</v>
       </c>
